--- a/it_forms/004_software_development_assessment--it_forms.xlsx
+++ b/it_forms/004_software_development_assessment--it_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>software_development_assessment_page</t>
+          <t>overview</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Software Development Assessment</t>
+          <t>Software Development Overview</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,58 +543,58 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>experience</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Experience</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>languages</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Programming Languages</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>software_development_assessment_page_1</t>
+          <t>agile</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Software Development Assessment</t>
+          <t>Agile Experience</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>tools</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Development Tools</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>category_1</t>
+          <t>frameworks</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Frameworks and Libraries</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>description_1</t>
+          <t>devops</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>DevOps and CI/CD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>software_development_assessment_page_2</t>
+          <t>projects</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Software Development Assessment</t>
+          <t>Project Experience</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>category_2</t>
+          <t>cloud</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Cloud Computing</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,21 +722,67 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>description_2</t>
+          <t>operating_systems</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Operating Systems</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>sdlc</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Software Development Life Cycle (SDLC)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>comments</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Comments</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -753,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -781,102 +827,595 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>experience_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>it_forms</t>
+          <t>junior</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IT Forms</t>
+          <t>Junior</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>experience_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>mid-level</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Mid-Level</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>category_1_choices</t>
+          <t>experience_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>it_forms</t>
+          <t>senior</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>IT Forms</t>
+          <t>Senior</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>category_1_choices</t>
+          <t>languages_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>java</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Java</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>category_2_choices</t>
+          <t>languages_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>it_forms</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>IT Forms</t>
+          <t>Python</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>category_2_choices</t>
+          <t>languages_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>c++</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>C++</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>languages_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>c#</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>languages_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>javascript</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>JavaScript</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>languages_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>sql</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tools_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>eclipse</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Eclipse</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tools_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>visual_studio</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Visual Studio</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>tools_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>intellij</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>IntelliJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>tools_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>sublime_text</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Sublime Text</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>tools_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>atom</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Atom</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>frameworks_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>spring</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Spring</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>frameworks_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>django</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Django</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>frameworks_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>react</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>React</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>frameworks_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>angular</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Angular</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>frameworks_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>vue</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Vue</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>frameworks_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>express</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Express</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>devops_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>jenkins</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Jenkins</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>devops_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Git</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>devops_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>docker</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Docker</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>devops_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>kubernetes</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Kubernetes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>devops_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>nagios</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Nagios</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>devops_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>circleci</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CircleCI</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cloud_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>aws</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cloud_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>azure</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Azure</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cloud_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>google_cloud</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Google Cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>cloud_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>on-premises</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>On-premises</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>operating_systems_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>windows</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>operating_systems_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>linux</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Linux</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>operating_systems_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>macos</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>macOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>operating_systems_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>unix</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Unix</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>operating_systems_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>solaris</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Solaris</t>
         </is>
       </c>
     </row>
